--- a/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_04.xlsx
+++ b/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_04.xlsx
@@ -670,7 +670,7 @@
     <t>Krstovic</t>
   </si>
   <si>
-    <t>D'aversa</t>
+    <t>D'Aversa</t>
   </si>
   <si>
     <t>Milan</t>
@@ -820,7 +820,7 @@
     <t>Zerbin</t>
   </si>
   <si>
-    <t xml:space="preserve">Cajuste </t>
+    <t>Cajuste</t>
   </si>
   <si>
     <t>Raspadori</t>
@@ -847,7 +847,7 @@
     <t>Mancini</t>
   </si>
   <si>
-    <t>N'dicka</t>
+    <t>N'Dicka</t>
   </si>
   <si>
     <t>Llorente D.</t>
@@ -1282,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:O382"/>
+  <dimension ref="A1:M382"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1425,8 +1425,6 @@
       <c r="M6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -2182,8 +2180,6 @@
       <c r="M25" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
     </row>
     <row r="26">
       <c r="A26" s="12">
@@ -2939,8 +2935,6 @@
       <c r="M44" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
     </row>
     <row r="45">
       <c r="A45" s="0">
@@ -3696,8 +3690,6 @@
       <c r="M63" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N63" s="9"/>
-      <c r="O63" s="9"/>
     </row>
     <row r="64">
       <c r="A64" s="12">
@@ -4453,8 +4445,6 @@
       <c r="M82" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N82" s="9"/>
-      <c r="O82" s="9"/>
     </row>
     <row r="83">
       <c r="A83" s="0">
@@ -5210,8 +5200,6 @@
       <c r="M101" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="9"/>
-      <c r="O101" s="9"/>
     </row>
     <row r="102">
       <c r="A102" s="12">
@@ -5967,8 +5955,6 @@
       <c r="M120" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N120" s="9"/>
-      <c r="O120" s="9"/>
     </row>
     <row r="121">
       <c r="A121" s="0">
@@ -6642,8 +6628,6 @@
       <c r="M137" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N137" s="9"/>
-      <c r="O137" s="9"/>
     </row>
     <row r="138">
       <c r="A138" s="12">
@@ -7399,8 +7383,6 @@
       <c r="M156" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N156" s="9"/>
-      <c r="O156" s="9"/>
     </row>
     <row r="157">
       <c r="A157" s="0">
@@ -8156,8 +8138,6 @@
       <c r="M175" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N175" s="9"/>
-      <c r="O175" s="9"/>
     </row>
     <row r="176">
       <c r="A176" s="12">
@@ -8913,8 +8893,6 @@
       <c r="M194" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N194" s="9"/>
-      <c r="O194" s="9"/>
     </row>
     <row r="195">
       <c r="A195" s="0">
@@ -9670,8 +9648,6 @@
       <c r="M213" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N213" s="9"/>
-      <c r="O213" s="9"/>
     </row>
     <row r="214">
       <c r="A214" s="12">
@@ -10427,8 +10403,6 @@
       <c r="M232" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N232" s="9"/>
-      <c r="O232" s="9"/>
     </row>
     <row r="233">
       <c r="A233" s="0">
@@ -11184,8 +11158,6 @@
       <c r="M251" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N251" s="9"/>
-      <c r="O251" s="9"/>
     </row>
     <row r="252">
       <c r="A252" s="12">
@@ -11941,8 +11913,6 @@
       <c r="M270" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N270" s="9"/>
-      <c r="O270" s="9"/>
     </row>
     <row r="271">
       <c r="A271" s="0">
@@ -12698,8 +12668,6 @@
       <c r="M289" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N289" s="9"/>
-      <c r="O289" s="9"/>
     </row>
     <row r="290">
       <c r="A290" s="12">
@@ -13455,8 +13423,6 @@
       <c r="M308" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N308" s="9"/>
-      <c r="O308" s="9"/>
     </row>
     <row r="309">
       <c r="A309" s="0">
@@ -14212,8 +14178,6 @@
       <c r="M327" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N327" s="9"/>
-      <c r="O327" s="9"/>
     </row>
     <row r="328">
       <c r="A328" s="12">
@@ -14969,8 +14933,6 @@
       <c r="M346" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N346" s="9"/>
-      <c r="O346" s="9"/>
     </row>
     <row r="347">
       <c r="A347" s="0">
@@ -15726,8 +15688,6 @@
       <c r="M365" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N365" s="9"/>
-      <c r="O365" s="9"/>
     </row>
     <row r="366">
       <c r="A366" s="12">
@@ -16459,7 +16419,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:O382"/>
+  <dimension ref="A1:M382"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -16602,8 +16562,6 @@
       <c r="M6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -17359,8 +17317,6 @@
       <c r="M25" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
     </row>
     <row r="26">
       <c r="A26" s="12">
@@ -18116,8 +18072,6 @@
       <c r="M44" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
     </row>
     <row r="45">
       <c r="A45" s="0">
@@ -18873,8 +18827,6 @@
       <c r="M63" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N63" s="9"/>
-      <c r="O63" s="9"/>
     </row>
     <row r="64">
       <c r="A64" s="12">
@@ -19630,8 +19582,6 @@
       <c r="M82" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N82" s="9"/>
-      <c r="O82" s="9"/>
     </row>
     <row r="83">
       <c r="A83" s="0">
@@ -20387,8 +20337,6 @@
       <c r="M101" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="9"/>
-      <c r="O101" s="9"/>
     </row>
     <row r="102">
       <c r="A102" s="12">
@@ -21144,8 +21092,6 @@
       <c r="M120" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N120" s="9"/>
-      <c r="O120" s="9"/>
     </row>
     <row r="121">
       <c r="A121" s="0">
@@ -21819,8 +21765,6 @@
       <c r="M137" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N137" s="9"/>
-      <c r="O137" s="9"/>
     </row>
     <row r="138">
       <c r="A138" s="12">
@@ -22576,8 +22520,6 @@
       <c r="M156" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N156" s="9"/>
-      <c r="O156" s="9"/>
     </row>
     <row r="157">
       <c r="A157" s="0">
@@ -23333,8 +23275,6 @@
       <c r="M175" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N175" s="9"/>
-      <c r="O175" s="9"/>
     </row>
     <row r="176">
       <c r="A176" s="12">
@@ -24090,8 +24030,6 @@
       <c r="M194" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N194" s="9"/>
-      <c r="O194" s="9"/>
     </row>
     <row r="195">
       <c r="A195" s="0">
@@ -24847,8 +24785,6 @@
       <c r="M213" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N213" s="9"/>
-      <c r="O213" s="9"/>
     </row>
     <row r="214">
       <c r="A214" s="12">
@@ -25604,8 +25540,6 @@
       <c r="M232" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N232" s="9"/>
-      <c r="O232" s="9"/>
     </row>
     <row r="233">
       <c r="A233" s="0">
@@ -26361,8 +26295,6 @@
       <c r="M251" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N251" s="9"/>
-      <c r="O251" s="9"/>
     </row>
     <row r="252">
       <c r="A252" s="12">
@@ -27118,8 +27050,6 @@
       <c r="M270" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N270" s="9"/>
-      <c r="O270" s="9"/>
     </row>
     <row r="271">
       <c r="A271" s="0">
@@ -27875,8 +27805,6 @@
       <c r="M289" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N289" s="9"/>
-      <c r="O289" s="9"/>
     </row>
     <row r="290">
       <c r="A290" s="12">
@@ -28632,8 +28560,6 @@
       <c r="M308" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N308" s="9"/>
-      <c r="O308" s="9"/>
     </row>
     <row r="309">
       <c r="A309" s="0">
@@ -29389,8 +29315,6 @@
       <c r="M327" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N327" s="9"/>
-      <c r="O327" s="9"/>
     </row>
     <row r="328">
       <c r="A328" s="12">
@@ -30146,8 +30070,6 @@
       <c r="M346" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N346" s="9"/>
-      <c r="O346" s="9"/>
     </row>
     <row r="347">
       <c r="A347" s="0">
@@ -30903,8 +30825,6 @@
       <c r="M365" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N365" s="9"/>
-      <c r="O365" s="9"/>
     </row>
     <row r="366">
       <c r="A366" s="12">
@@ -31636,7 +31556,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:O382"/>
+  <dimension ref="A1:M382"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -31779,8 +31699,6 @@
       <c r="M6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -32536,8 +32454,6 @@
       <c r="M25" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
     </row>
     <row r="26">
       <c r="A26" s="12">
@@ -33293,8 +33209,6 @@
       <c r="M44" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
     </row>
     <row r="45">
       <c r="A45" s="0">
@@ -34050,8 +33964,6 @@
       <c r="M63" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N63" s="9"/>
-      <c r="O63" s="9"/>
     </row>
     <row r="64">
       <c r="A64" s="12">
@@ -34807,8 +34719,6 @@
       <c r="M82" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N82" s="9"/>
-      <c r="O82" s="9"/>
     </row>
     <row r="83">
       <c r="A83" s="0">
@@ -35564,8 +35474,6 @@
       <c r="M101" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="9"/>
-      <c r="O101" s="9"/>
     </row>
     <row r="102">
       <c r="A102" s="12">
@@ -36321,8 +36229,6 @@
       <c r="M120" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N120" s="9"/>
-      <c r="O120" s="9"/>
     </row>
     <row r="121">
       <c r="A121" s="0">
@@ -36996,8 +36902,6 @@
       <c r="M137" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N137" s="9"/>
-      <c r="O137" s="9"/>
     </row>
     <row r="138">
       <c r="A138" s="12">
@@ -37753,8 +37657,6 @@
       <c r="M156" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N156" s="9"/>
-      <c r="O156" s="9"/>
     </row>
     <row r="157">
       <c r="A157" s="0">
@@ -38510,8 +38412,6 @@
       <c r="M175" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N175" s="9"/>
-      <c r="O175" s="9"/>
     </row>
     <row r="176">
       <c r="A176" s="12">
@@ -39267,8 +39167,6 @@
       <c r="M194" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N194" s="9"/>
-      <c r="O194" s="9"/>
     </row>
     <row r="195">
       <c r="A195" s="0">
@@ -40024,8 +39922,6 @@
       <c r="M213" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N213" s="9"/>
-      <c r="O213" s="9"/>
     </row>
     <row r="214">
       <c r="A214" s="12">
@@ -40781,8 +40677,6 @@
       <c r="M232" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N232" s="9"/>
-      <c r="O232" s="9"/>
     </row>
     <row r="233">
       <c r="A233" s="0">
@@ -41538,8 +41432,6 @@
       <c r="M251" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N251" s="9"/>
-      <c r="O251" s="9"/>
     </row>
     <row r="252">
       <c r="A252" s="12">
@@ -42295,8 +42187,6 @@
       <c r="M270" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N270" s="9"/>
-      <c r="O270" s="9"/>
     </row>
     <row r="271">
       <c r="A271" s="0">
@@ -43052,8 +42942,6 @@
       <c r="M289" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N289" s="9"/>
-      <c r="O289" s="9"/>
     </row>
     <row r="290">
       <c r="A290" s="12">
@@ -43809,8 +43697,6 @@
       <c r="M308" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N308" s="9"/>
-      <c r="O308" s="9"/>
     </row>
     <row r="309">
       <c r="A309" s="0">
@@ -44566,8 +44452,6 @@
       <c r="M327" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N327" s="9"/>
-      <c r="O327" s="9"/>
     </row>
     <row r="328">
       <c r="A328" s="12">
@@ -45323,8 +45207,6 @@
       <c r="M346" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N346" s="9"/>
-      <c r="O346" s="9"/>
     </row>
     <row r="347">
       <c r="A347" s="0">
@@ -46080,8 +45962,6 @@
       <c r="M365" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N365" s="9"/>
-      <c r="O365" s="9"/>
     </row>
     <row r="366">
       <c r="A366" s="12">
